--- a/data/trans_dic/IP25B_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25B_1_R-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,88</t>
+          <t>1,49; 13,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,43</t>
+          <t>1,36; 7,99</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,56</t>
+          <t>4,81; 12,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 19,27</t>
+          <t>9,35; 18,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 14,23</t>
+          <t>8,18; 14,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,86; 31,42</t>
+          <t>18,64; 31,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,92</t>
+          <t>13,64; 23,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 25,42</t>
+          <t>17,7; 25,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 57,26</t>
+          <t>30,01; 56,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,33; 47,36</t>
+          <t>32,75; 47,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,36; 48,39</t>
+          <t>33,59; 47,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,3; 35,17</t>
+          <t>20,23; 35,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,44</t>
+          <t>20,88; 28,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,93</t>
+          <t>21,82; 29,72</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2070</t>
+          <t>0; 2203</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>906; 7519</t>
+          <t>872; 7900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1140; 8172</t>
+          <t>1501; 8790</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7683; 19481</t>
+          <t>7464; 18714</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17379; 35087</t>
+          <t>17027; 34009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28632; 47973</t>
+          <t>27561; 47927</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32640; 54381</t>
+          <t>32264; 54047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28966; 48693</t>
+          <t>28989; 49683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67157; 97995</t>
+          <t>68245; 99201</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81482; 155340</t>
+          <t>81427; 154236</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97668; 143095</t>
+          <t>98950; 144499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>191294; 277472</t>
+          <t>192634; 274903</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>132180; 228954</t>
+          <t>131679; 231542</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156383; 214708</t>
+          <t>157692; 216130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>305178; 420889</t>
+          <t>306744; 417915</t>
         </is>
       </c>
     </row>
